--- a/해커톤 AI에이전트/results/live_sim/line_sim_accuracy.xlsx
+++ b/해커톤 AI에이전트/results/live_sim/line_sim_accuracy.xlsx
@@ -9,7 +9,8 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="By defect type" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Definitions" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Routing (mixed line)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Definitions" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -452,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:O5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -469,6 +470,7 @@
     <col width="8" customWidth="1" min="12" max="12"/>
     <col width="18" customWidth="1" min="13" max="13"/>
     <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -542,6 +544,11 @@
           <t>Processing capacity</t>
         </is>
       </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Routing accuracy</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -604,6 +611,11 @@
           <t>61.4 fps</t>
         </is>
       </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -666,6 +678,11 @@
           <t>64.0 fps</t>
         </is>
       </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -726,6 +743,78 @@
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>48.3 fps</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>172.8 s</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>95.6%</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>74/76</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>12/14</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>46 / 30 / 14</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>283 / 3 / 2</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>0.993</v>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>0.991</v>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>11.5 / 31.5</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>87.1 fps</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1759,145 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Product (ground truth)</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Items</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Routed correctly</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Routing accuracy</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Verdict correct</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Rules used</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>LCD</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>wide 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Metal</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>93.3%</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>dark 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>PCB</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>93.3%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>green 30</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1752,10 +1979,22 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
+          <t>Routing accuracy</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Mixed line only: the dispatcher (agent/line_router.py) picks the product type from the item box (aspect ratio, green ratio, dark ratio) before cropping and inspecting with the model for that type.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
           <t>Processing ms/frame</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Time for one frame: product finding, sensing-zone inspection when an item passes, full-frame preview detection and drawing (RTX 5060 Laptop GPU). Video encoding excluded.</t>
         </is>
